--- a/DocumentoEngenharia/Book 3.xlsx
+++ b/DocumentoEngenharia/Book 3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20A68051-73F8-45F7-ADFA-A5562E5E74AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1BFA0E3-46B9-4C48-AE91-91145ABDD727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
     <t>id*</t>
   </si>
   <si>
-    <t>Nome</t>
+    <t>Nome do requisito</t>
   </si>
   <si>
     <t>Descrição das regras de domínio</t>
@@ -68,7 +68,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -78,6 +78,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -122,11 +128,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,9 +465,10 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">

--- a/DocumentoEngenharia/Book 3.xlsx
+++ b/DocumentoEngenharia/Book 3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1BFA0E3-46B9-4C48-AE91-91145ABDD727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6847CB8-BFD8-493F-B3B6-AA8FE2940D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,13 +36,34 @@
     <t>LISTA DE REQUISITOS - PROJETO DO SISTEMA DE ESTACIONAMENTO</t>
   </si>
   <si>
-    <t>*Legenda: Rf = requisito funcional; Rnf = requisito não funcional</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Legenda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Rf = requisito funcional; Rnf = requisito não funcional</t>
+    </r>
   </si>
   <si>
     <t>id*</t>
   </si>
   <si>
-    <t>Nome do requisito</t>
+    <t>Nome</t>
   </si>
   <si>
     <t>Descrição das regras de domínio</t>
@@ -52,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +84,27 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -83,7 +125,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -128,12 +170,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,15 +504,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
